--- a/demo/CONFUNFIS_DEMO_TRAMONTANA.xlsx
+++ b/demo/CONFUNFIS_DEMO_TRAMONTANA.xlsx
@@ -4592,7 +4592,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
